--- a/Laska_etal_2008/Laska_etal_2008_registry_rows.xlsx
+++ b/Laska_etal_2008/Laska_etal_2008_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rf9dfc56f8dd44222"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Ra05515771a1744d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R60355a23e77f4f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R81b018b4b3034090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R39ed1208f45f4bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R474e0c52baf1456c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>MSG and sodium-chloride concentration discrimination; Weber ratios</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Figure 5: Individual MSG and NaCl difference thresholds at four reference concentrations</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — optional taste extension; gap required
@@ -350,13 +350,13 @@
         <x:v>Source citation and endpoint in existing source notes; Nick/Fran dissertation reference check.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 6 / printed p. 844. Weber ratios for each individual and compound; keep reference concentration and species. Figures 1–4 show underlying discrimination curves and are not additional independent observations.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/2044897697/Laska-2008-Taste difference thresholds for mon.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +508,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Laska, M., Persson Suorra, J., Rivas Bautista, R. M., &amp; Hernandez Salazar, L. T. (2008). Taste difference thresholds for monosodium glutamate and sodium chloride in pigtail macaques (Macaca nemestrina) and spider monkeys (Ateles geoffroyi). American Journal of Primatology, 70(9), 839–847. https://doi.org/10.1002/ajp.20558</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Figure 5</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant addition; not found in dissertation references. Planned folder: Laska_etal_2008. Target: Source tables / results to select. Keep just-noticeable differences separate from preference/avoidance thresholds. Preserve reference concentration (50, 100, 200, 400 mM).
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 6 / printed p. 844. Weber ratios for each individual and compound; keep reference concentration and species. Figures 1–4 show underlying discrimination curves and are not additional independent observations. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/2044897697/Laska-2008-Taste difference thresholds for mon.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — optional taste extension; gap required</x:v>
@@ -550,7 +552,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>MSG and sodium-chloride concentration discrimination; Weber ratios</x:v>
+        <x:v>Individual MSG and NaCl difference thresholds at four reference concentrations</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -695,7 +697,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="100" customHeight="1">
@@ -703,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -987,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5DB0FA3-DF88-4A48-8E1B-18ADB526A4BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C199980-9741-4021-B6D0-DC3773ADEE41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156A1231-2823-4BFA-898A-52B463E5CFD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0167EAFF-9364-44C8-A4B1-1BC3E8C5C359}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{657ECDC1-8A1E-44F2-8E5D-34ADEFB9B3BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BC0C096-3DAD-48FF-A264-03F5A847DB45}"/>
 </file>